--- a/reports/pdf_change_20260708.xlsx
+++ b/reports/pdf_change_20260708.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,102억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 5종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,034억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 5종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1100389950</v>
+        <v>1101423180</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-37</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1306275750</v>
+        <v>-1307502300</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>996840000</v>
+        <v>997776000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-36</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1023678000</v>
+        <v>-1024639200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>544747500</v>
+        <v>545259000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-17</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-993964500</v>
+        <v>-994897800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>470730000</v>
+        <v>471172000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-948382500</v>
+        <v>-949273000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>438247500</v>
+        <v>438659000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-11</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1320280500</v>
+        <v>-1321520200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-8</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1378536000</v>
+        <v>-1379830400</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>-7</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1015371000</v>
+        <v>-1016324400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,517억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,657억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -963,7 +963,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,251억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 2종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,176억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1059,7 +1059,7 @@
         <v>221</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>7979569650</v>
+        <v>8030786400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>-56</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-6325480000</v>
+        <v>-6366080000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>30</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>7957485000</v>
+        <v>8008560000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>-49</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1421869750</v>
+        <v>-1430996000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>-36</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-3160558800</v>
+        <v>-3180844800</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>-20</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2181200000</v>
+        <v>-2195200000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,694억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,760억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1220,7 +1220,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 356억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 4종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1316,11 +1316,11 @@
         <v>18</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>143614800</v>
+        <v>131846400</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>3.46%→3.86%</t>
+          <t>3.22%→3.59%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1337,11 +1337,11 @@
         <v>-318</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-105738180</v>
+        <v>-105245280</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2.93%→2.62%</t>
+          <t>2.96%→2.64%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1360,11 +1360,11 @@
         <v>16</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>42836800</v>
+        <v>44284800</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>0.16%→0.29%</t>
+          <t>0.17%→0.30%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1381,11 +1381,11 @@
         <v>-25</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-70827500</v>
+        <v>-74130000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>6.00%→5.77%</t>
+          <t>6.36%→6.13%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1404,11 +1404,11 @@
         <v>13</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>170986400</v>
+        <v>158340000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2.85%→3.33%</t>
+          <t>2.67%→3.13%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1425,11 +1425,11 @@
         <v>-10</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-62238000</v>
+        <v>-71652000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>0.86%→0.68%</t>
+          <t>1.01%→0.80%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1448,11 +1448,11 @@
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>74538000</v>
+        <v>70560000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.50%</t>
+          <t>1.24%→1.44%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1469,11 +1469,11 @@
         <v>-7</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-73012800</v>
+        <v>-75028800</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>3.22%→3.00%</t>
+          <t>3.36%→3.13%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>

--- a/reports/pdf_change_20260708.xlsx
+++ b/reports/pdf_change_20260708.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 6/7  ·  대기: TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -1218,331 +1218,81 @@
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="20" t="n"/>
+      <c r="K28" s="20" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>131846400</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>3.22%→3.59%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>150→168</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-318</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-105245280</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>2.96%→2.64%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>3,054→2,736</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>44284800</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>0.17%→0.30%</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>21→37</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>-74130000</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>6.36%→6.13%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>733→708</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>158340000</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>2.67%→3.13%</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>75→88</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>-71652000</v>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>1.01%→0.80%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>48→38</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>70560000</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>1.24%→1.44%</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>36→42</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>-75028800</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>3.36%→3.13%</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>107→100</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="20" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="20" t="n"/>
+      <c r="K33" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="16">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G29:K29"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A33:K33"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260708.xlsx
+++ b/reports/pdf_change_20260708.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1218,81 +1218,331 @@
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>131846400</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>3.22%→3.59%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>150→168</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-318</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-105245280</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>2.96%→2.64%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>3,054→2,736</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>44284800</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>0.17%→0.30%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>21→37</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-74130000</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>6.36%→6.13%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>733→708</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>158340000</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2.67%→3.13%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>75→88</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-71652000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>1.01%→0.80%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>48→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>70560000</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>1.24%→1.44%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>36→42</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-75028800</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>3.36%→3.13%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>107→100</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      당일 2026-07-08  vs  전영업일 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="20" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="20" t="n"/>
-      <c r="I33" s="20" t="n"/>
-      <c r="J33" s="20" t="n"/>
-      <c r="K33" s="20" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="20" t="n"/>
+      <c r="K39" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G29:K29"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A33:K33"/>
     <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
